--- a/data_voor_swing/aggregatietabellen/statsec2024_kerntypering.xlsx
+++ b/data_voor_swing/aggregatietabellen/statsec2024_kerntypering.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19438" uniqueCount="10247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19437" uniqueCount="10246">
   <si>
     <t>statsec2024</t>
   </si>
@@ -30752,9 +30752,6 @@
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>99999</t>
   </si>
 </sst>
 </file>
@@ -109894,9 +109891,6 @@
       <c r="A10239" t="s">
         <v>10239</v>
       </c>
-      <c r="B10239" t="s">
-        <v>10246</v>
-      </c>
     </row>
     <row r="10240" spans="1:2">
       <c r="A10240" t="s">
